--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0829DA-0647-4ADF-841F-FFA9DA181A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65F5E99-8612-428D-A9EC-E1362255F635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -1166,392 +1166,212 @@
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="7">
-        <v>1267213</v>
-      </c>
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="7">
-        <v>621781</v>
-      </c>
+      <c r="A23" s="6"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="7">
-        <v>630651</v>
-      </c>
+      <c r="A24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="7">
-        <v>692423</v>
-      </c>
+      <c r="A25" s="6"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="7">
-        <v>526545</v>
-      </c>
+      <c r="A26" s="6"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="7">
-        <v>726344</v>
-      </c>
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="7">
-        <v>787273</v>
-      </c>
+      <c r="A28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="7">
-        <v>807782</v>
-      </c>
+      <c r="A29" s="6"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="7">
-        <v>680582</v>
-      </c>
+      <c r="A30" s="6"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="7">
-        <v>645953</v>
-      </c>
+      <c r="A31" s="6"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="7">
-        <v>386633</v>
-      </c>
+      <c r="A32" s="6"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="7">
-        <v>294302</v>
-      </c>
+      <c r="A33" s="6"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="7">
-        <v>487075</v>
-      </c>
+      <c r="A34" s="6"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="7">
-        <v>550203</v>
-      </c>
+      <c r="A35" s="6"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="7">
-        <v>490054</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="7">
-        <v>548324</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="7">
-        <v>661997</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="7">
-        <v>658299</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="7">
-        <v>525263</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="7">
-        <v>525263</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="7">
-        <v>510004</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="7">
-        <v>767862</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="7">
-        <v>740306</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="7">
-        <v>573223</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="7">
-        <v>461695</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="7">
-        <v>416102</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="7">
-        <v>461103</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="7">
-        <v>603442</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="7">
-        <v>526308</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="7">
-        <v>676261</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1228</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,15 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,9 +232,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,39 +247,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,10 +285,26 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -319,7 +318,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,21 +326,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,37 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,19 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,30 +587,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -638,6 +614,41 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -657,162 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1228"/>
+  <dimension ref="A1:E1229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16683,9 +16683,20 @@
         <v>330735</v>
       </c>
     </row>
+    <row r="1229" spans="1:3">
+      <c r="A1229" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1229">
+        <v>398760</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1227">
-    <sortState ref="A1:E1227">
+  <autoFilter ref="A1:E1228">
+    <sortState ref="A1:E1228">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1144</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,23 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,8 +232,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,14 +264,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,11 +277,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,15 +293,23 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,16 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -610,15 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -636,20 +627,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,70 +648,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -743,92 +743,92 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1229"/>
+  <dimension ref="A1:E1144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16122,587 +16122,37 @@
       <c r="D1142" s="8"/>
       <c r="E1142" s="9"/>
     </row>
-    <row r="1143" spans="1:5">
-      <c r="A1143" s="4"/>
-      <c r="B1143" s="5"/>
-      <c r="C1143" s="8"/>
-      <c r="D1143" s="8"/>
-      <c r="E1143" s="9"/>
-    </row>
-    <row r="1144" spans="1:5">
-      <c r="A1144" s="4"/>
-      <c r="B1144" s="5"/>
-      <c r="C1144" s="8"/>
-      <c r="D1144" s="8"/>
-      <c r="E1144" s="9"/>
-    </row>
-    <row r="1145" spans="1:5">
-      <c r="A1145" s="4"/>
-      <c r="B1145" s="5"/>
-      <c r="C1145" s="8"/>
-      <c r="D1145" s="8"/>
-      <c r="E1145" s="9"/>
-    </row>
-    <row r="1146" spans="1:5">
-      <c r="A1146" s="4"/>
-      <c r="B1146" s="5"/>
-      <c r="C1146" s="8"/>
-      <c r="D1146" s="8"/>
-      <c r="E1146" s="9"/>
-    </row>
-    <row r="1147" spans="1:5">
-      <c r="A1147" s="4"/>
-      <c r="B1147" s="5"/>
-      <c r="C1147" s="8"/>
-      <c r="D1147" s="8"/>
-      <c r="E1147" s="9"/>
-    </row>
-    <row r="1148" spans="1:5">
-      <c r="A1148" s="4"/>
-      <c r="B1148" s="5"/>
-      <c r="C1148" s="8"/>
-      <c r="D1148" s="8"/>
-      <c r="E1148" s="9"/>
-    </row>
-    <row r="1149" spans="1:5">
-      <c r="A1149" s="4"/>
-      <c r="B1149" s="5"/>
-      <c r="C1149" s="8"/>
-      <c r="D1149" s="8"/>
-      <c r="E1149" s="9"/>
-    </row>
-    <row r="1150" spans="1:5">
-      <c r="A1150" s="4"/>
-      <c r="B1150" s="5"/>
-      <c r="C1150" s="8"/>
-      <c r="D1150" s="8"/>
-      <c r="E1150" s="9"/>
-    </row>
-    <row r="1151" spans="1:5">
-      <c r="A1151" s="4"/>
-      <c r="B1151" s="5"/>
-      <c r="C1151" s="8"/>
-      <c r="D1151" s="8"/>
-      <c r="E1151" s="9"/>
-    </row>
-    <row r="1152" spans="1:5">
-      <c r="A1152" s="4"/>
-      <c r="B1152" s="5"/>
-      <c r="C1152" s="8"/>
-      <c r="D1152" s="8"/>
-      <c r="E1152" s="9"/>
-    </row>
-    <row r="1153" spans="1:5">
-      <c r="A1153" s="4"/>
-      <c r="B1153" s="5"/>
-      <c r="C1153" s="8"/>
-      <c r="D1153" s="8"/>
-      <c r="E1153" s="9"/>
-    </row>
-    <row r="1154" spans="1:5">
-      <c r="A1154" s="4"/>
-      <c r="B1154" s="5"/>
-      <c r="C1154" s="8"/>
-      <c r="D1154" s="8"/>
-      <c r="E1154" s="9"/>
-    </row>
-    <row r="1155" spans="1:5">
-      <c r="A1155" s="4"/>
-      <c r="B1155" s="5"/>
-      <c r="C1155" s="8"/>
-      <c r="D1155" s="8"/>
-      <c r="E1155" s="9"/>
-    </row>
-    <row r="1156" spans="1:5">
-      <c r="A1156" s="4"/>
-      <c r="B1156" s="5"/>
-      <c r="C1156" s="8"/>
-      <c r="D1156" s="8"/>
-      <c r="E1156" s="9"/>
-    </row>
-    <row r="1157" spans="1:5">
-      <c r="A1157" s="4"/>
-      <c r="B1157" s="5"/>
-      <c r="C1157" s="8"/>
-      <c r="D1157" s="8"/>
-      <c r="E1157" s="9"/>
-    </row>
-    <row r="1158" spans="1:5">
-      <c r="A1158" s="4"/>
-      <c r="B1158" s="5"/>
-      <c r="C1158" s="8"/>
-      <c r="D1158" s="8"/>
-      <c r="E1158" s="9"/>
-    </row>
-    <row r="1159" spans="1:5">
-      <c r="A1159" s="4"/>
-      <c r="B1159" s="5"/>
-      <c r="C1159" s="8"/>
-      <c r="D1159" s="8"/>
-      <c r="E1159" s="9"/>
-    </row>
-    <row r="1160" spans="1:5">
-      <c r="A1160" s="4"/>
-      <c r="B1160" s="5"/>
-      <c r="C1160" s="8"/>
-      <c r="D1160" s="8"/>
-      <c r="E1160" s="9"/>
-    </row>
-    <row r="1161" spans="1:5">
-      <c r="A1161" s="4"/>
-      <c r="B1161" s="5"/>
-      <c r="C1161" s="8"/>
-      <c r="D1161" s="8"/>
-      <c r="E1161" s="9"/>
-    </row>
-    <row r="1162" spans="1:5">
-      <c r="A1162" s="4"/>
-      <c r="B1162" s="5"/>
-      <c r="C1162" s="8"/>
-      <c r="D1162" s="8"/>
-      <c r="E1162" s="9"/>
-    </row>
-    <row r="1163" spans="1:5">
-      <c r="A1163" s="4"/>
-      <c r="B1163" s="5"/>
-      <c r="C1163" s="8"/>
-      <c r="D1163" s="8"/>
-      <c r="E1163" s="9"/>
-    </row>
-    <row r="1164" spans="1:5">
-      <c r="A1164" s="7"/>
-      <c r="B1164" s="5"/>
-      <c r="C1164" s="8"/>
-      <c r="D1164" s="8"/>
-      <c r="E1164" s="9"/>
-    </row>
-    <row r="1165" spans="1:5">
-      <c r="A1165" s="4"/>
-      <c r="B1165" s="5"/>
-      <c r="C1165" s="8"/>
-      <c r="D1165" s="8"/>
-      <c r="E1165" s="9"/>
-    </row>
-    <row r="1166" spans="1:5">
-      <c r="A1166" s="4"/>
-      <c r="B1166" s="5"/>
-      <c r="C1166" s="8"/>
-      <c r="D1166" s="8"/>
-      <c r="E1166" s="9"/>
-    </row>
-    <row r="1167" spans="1:5">
-      <c r="A1167" s="4"/>
-      <c r="B1167" s="5"/>
-      <c r="C1167" s="8"/>
-      <c r="D1167" s="8"/>
-      <c r="E1167" s="9"/>
-    </row>
-    <row r="1168" spans="1:5">
-      <c r="A1168" s="4"/>
-      <c r="B1168" s="5"/>
-      <c r="C1168" s="8"/>
-      <c r="D1168" s="8"/>
-      <c r="E1168" s="9"/>
-    </row>
-    <row r="1169" spans="1:5">
-      <c r="A1169" s="4"/>
-      <c r="B1169" s="5"/>
-      <c r="C1169" s="8"/>
-      <c r="D1169" s="8"/>
-      <c r="E1169" s="9"/>
-    </row>
-    <row r="1170" spans="1:5">
-      <c r="A1170" s="4"/>
-      <c r="B1170" s="5"/>
-      <c r="C1170" s="8"/>
-      <c r="D1170" s="8"/>
-      <c r="E1170" s="9"/>
-    </row>
-    <row r="1171" spans="1:5">
-      <c r="A1171" s="4"/>
-      <c r="B1171" s="5"/>
-      <c r="C1171" s="8"/>
-      <c r="D1171" s="8"/>
-      <c r="E1171" s="9"/>
-    </row>
-    <row r="1172" spans="1:5">
-      <c r="A1172" s="4"/>
-      <c r="B1172" s="5"/>
-      <c r="C1172" s="8"/>
-      <c r="D1172" s="8"/>
-      <c r="E1172" s="9"/>
-    </row>
-    <row r="1173" spans="1:5">
-      <c r="A1173" s="4"/>
-      <c r="B1173" s="5"/>
-      <c r="C1173" s="8"/>
-      <c r="D1173" s="8"/>
-      <c r="E1173" s="9"/>
-    </row>
-    <row r="1174" spans="1:5">
-      <c r="A1174" s="4"/>
-      <c r="B1174" s="5"/>
-      <c r="C1174" s="8"/>
-      <c r="D1174" s="8"/>
-      <c r="E1174" s="9"/>
-    </row>
-    <row r="1175" spans="1:5">
-      <c r="A1175" s="4"/>
-      <c r="B1175" s="5"/>
-      <c r="C1175" s="8"/>
-      <c r="D1175" s="8"/>
-      <c r="E1175" s="9"/>
-    </row>
-    <row r="1176" spans="1:5">
-      <c r="A1176" s="4"/>
-      <c r="B1176" s="5"/>
-      <c r="C1176" s="8"/>
-      <c r="D1176" s="8"/>
-      <c r="E1176" s="9"/>
-    </row>
-    <row r="1177" spans="1:5">
-      <c r="A1177" s="4"/>
-      <c r="B1177" s="5"/>
-      <c r="C1177" s="8"/>
-      <c r="D1177" s="8"/>
-      <c r="E1177" s="9"/>
-    </row>
-    <row r="1178" spans="1:5">
-      <c r="A1178" s="4"/>
-      <c r="B1178" s="5"/>
-      <c r="C1178" s="8"/>
-      <c r="D1178" s="8"/>
-      <c r="E1178" s="9"/>
-    </row>
-    <row r="1179" spans="1:5">
-      <c r="A1179" s="4"/>
-      <c r="B1179" s="5"/>
-      <c r="C1179" s="8"/>
-      <c r="D1179" s="8"/>
-      <c r="E1179" s="9"/>
-    </row>
-    <row r="1180" spans="1:5">
-      <c r="A1180" s="4"/>
-      <c r="B1180" s="5"/>
-      <c r="C1180" s="8"/>
-      <c r="D1180" s="8"/>
-      <c r="E1180" s="9"/>
-    </row>
-    <row r="1181" spans="1:5">
-      <c r="A1181" s="4"/>
-      <c r="B1181" s="5"/>
-      <c r="C1181" s="8"/>
-      <c r="D1181" s="8"/>
-      <c r="E1181" s="9"/>
-    </row>
-    <row r="1182" spans="1:5">
-      <c r="A1182" s="4"/>
-      <c r="B1182" s="5"/>
-      <c r="C1182" s="8"/>
-      <c r="D1182" s="8"/>
-      <c r="E1182" s="9"/>
-    </row>
-    <row r="1183" spans="1:5">
-      <c r="A1183" s="4"/>
-      <c r="B1183" s="5"/>
-      <c r="C1183" s="8"/>
-      <c r="D1183" s="8"/>
-      <c r="E1183" s="9"/>
-    </row>
-    <row r="1184" spans="1:5">
-      <c r="A1184" s="4"/>
-      <c r="B1184" s="5"/>
-      <c r="C1184" s="8"/>
-      <c r="D1184" s="8"/>
-      <c r="E1184" s="9"/>
-    </row>
-    <row r="1185" spans="1:5">
-      <c r="A1185" s="4"/>
-      <c r="B1185" s="5"/>
-      <c r="C1185" s="8"/>
-      <c r="D1185" s="8"/>
-      <c r="E1185" s="9"/>
-    </row>
-    <row r="1186" spans="1:5">
-      <c r="A1186" s="4"/>
-      <c r="B1186" s="5"/>
-      <c r="C1186" s="8"/>
-      <c r="D1186" s="8"/>
-      <c r="E1186" s="9"/>
-    </row>
-    <row r="1187" spans="1:5">
-      <c r="A1187" s="4"/>
-      <c r="B1187" s="5"/>
-      <c r="C1187" s="8"/>
-      <c r="D1187" s="8"/>
-      <c r="E1187" s="9"/>
-    </row>
-    <row r="1188" spans="1:5">
-      <c r="A1188" s="4"/>
-      <c r="B1188" s="5"/>
-      <c r="C1188" s="8"/>
-      <c r="D1188" s="8"/>
-      <c r="E1188" s="9"/>
-    </row>
-    <row r="1189" spans="1:5">
-      <c r="A1189" s="4"/>
-      <c r="B1189" s="5"/>
-      <c r="C1189" s="8"/>
-      <c r="D1189" s="8"/>
-      <c r="E1189" s="9"/>
-    </row>
-    <row r="1190" spans="1:5">
-      <c r="A1190" s="4"/>
-      <c r="B1190" s="5"/>
-      <c r="C1190" s="8"/>
-      <c r="D1190" s="8"/>
-      <c r="E1190" s="9"/>
-    </row>
-    <row r="1191" spans="1:5">
-      <c r="A1191" s="4"/>
-      <c r="B1191" s="5"/>
-      <c r="C1191" s="8"/>
-      <c r="D1191" s="8"/>
-      <c r="E1191" s="9"/>
-    </row>
-    <row r="1192" spans="1:5">
-      <c r="A1192" s="4"/>
-      <c r="B1192" s="5"/>
-      <c r="C1192" s="8"/>
-      <c r="D1192" s="8"/>
-      <c r="E1192" s="9"/>
-    </row>
-    <row r="1193" spans="1:5">
-      <c r="A1193" s="4"/>
-      <c r="B1193" s="5"/>
-      <c r="C1193" s="8"/>
-      <c r="D1193" s="8"/>
-      <c r="E1193" s="9"/>
-    </row>
-    <row r="1194" spans="1:5">
-      <c r="A1194" s="4"/>
-      <c r="B1194" s="5"/>
-      <c r="C1194" s="8"/>
-      <c r="D1194" s="8"/>
-      <c r="E1194" s="9"/>
-    </row>
-    <row r="1195" spans="1:5">
-      <c r="A1195" s="4"/>
-      <c r="B1195" s="5"/>
-      <c r="C1195" s="8"/>
-      <c r="D1195" s="8"/>
-      <c r="E1195" s="9"/>
-    </row>
-    <row r="1196" spans="1:5">
-      <c r="A1196" s="7"/>
-      <c r="B1196" s="5"/>
-      <c r="C1196" s="8"/>
-      <c r="D1196" s="8"/>
-      <c r="E1196" s="9"/>
-    </row>
-    <row r="1197" spans="1:5">
-      <c r="A1197" s="4"/>
-      <c r="B1197" s="5"/>
-      <c r="C1197" s="8"/>
-      <c r="D1197" s="8"/>
-      <c r="E1197" s="9"/>
-    </row>
-    <row r="1198" spans="1:5">
-      <c r="A1198" s="4"/>
-      <c r="B1198" s="5"/>
-      <c r="C1198" s="8"/>
-      <c r="D1198" s="8"/>
-      <c r="E1198" s="9"/>
-    </row>
-    <row r="1199" spans="1:5">
-      <c r="A1199" s="4"/>
-      <c r="B1199" s="5"/>
-      <c r="C1199" s="8"/>
-      <c r="D1199" s="8"/>
-      <c r="E1199" s="9"/>
-    </row>
-    <row r="1200" spans="1:5">
-      <c r="A1200" s="4"/>
-      <c r="B1200" s="5"/>
-      <c r="C1200" s="8"/>
-      <c r="D1200" s="8"/>
-      <c r="E1200" s="9"/>
-    </row>
-    <row r="1201" spans="1:5">
-      <c r="A1201" s="4"/>
-      <c r="B1201" s="5"/>
-      <c r="C1201" s="8"/>
-      <c r="D1201" s="8"/>
-      <c r="E1201" s="9"/>
-    </row>
-    <row r="1202" spans="1:5">
-      <c r="A1202" s="4"/>
-      <c r="B1202" s="5"/>
-      <c r="C1202" s="8"/>
-      <c r="D1202" s="8"/>
-      <c r="E1202" s="9"/>
-    </row>
-    <row r="1203" spans="1:5">
-      <c r="A1203" s="4"/>
-      <c r="B1203" s="5"/>
-      <c r="C1203" s="8"/>
-      <c r="D1203" s="8"/>
-      <c r="E1203" s="9"/>
-    </row>
-    <row r="1204" spans="1:5">
-      <c r="A1204" s="4"/>
-      <c r="B1204" s="5"/>
-      <c r="C1204" s="8"/>
-      <c r="D1204" s="8"/>
-      <c r="E1204" s="9"/>
-    </row>
-    <row r="1205" spans="1:5">
-      <c r="A1205" s="4"/>
-      <c r="B1205" s="5"/>
-      <c r="C1205" s="8"/>
-      <c r="D1205" s="8"/>
-      <c r="E1205" s="9"/>
-    </row>
-    <row r="1206" spans="1:5">
-      <c r="A1206" s="4"/>
-      <c r="B1206" s="5"/>
-      <c r="C1206" s="8"/>
-      <c r="D1206" s="8"/>
-      <c r="E1206" s="9"/>
-    </row>
-    <row r="1207" spans="1:5">
-      <c r="A1207" s="4"/>
-      <c r="B1207" s="5"/>
-      <c r="C1207" s="8"/>
-      <c r="D1207" s="8"/>
-      <c r="E1207" s="9"/>
-    </row>
-    <row r="1208" spans="1:5">
-      <c r="A1208" s="4"/>
-      <c r="B1208" s="5"/>
-      <c r="C1208" s="8"/>
-      <c r="D1208" s="8"/>
-      <c r="E1208" s="9"/>
-    </row>
-    <row r="1209" spans="1:5">
-      <c r="A1209" s="4"/>
-      <c r="B1209" s="5"/>
-      <c r="C1209" s="8"/>
-      <c r="D1209" s="8"/>
-      <c r="E1209" s="9"/>
-    </row>
-    <row r="1210" spans="1:5">
-      <c r="A1210" s="4"/>
-      <c r="B1210" s="5"/>
-      <c r="C1210" s="8"/>
-      <c r="D1210" s="8"/>
-      <c r="E1210" s="9"/>
-    </row>
-    <row r="1211" spans="1:5">
-      <c r="A1211" s="4"/>
-      <c r="B1211" s="5"/>
-      <c r="C1211" s="8"/>
-      <c r="D1211" s="8"/>
-      <c r="E1211" s="9"/>
-    </row>
-    <row r="1212" spans="1:5">
-      <c r="A1212" s="4"/>
-      <c r="B1212" s="5"/>
-      <c r="C1212" s="8"/>
-      <c r="D1212" s="8"/>
-      <c r="E1212" s="9"/>
-    </row>
-    <row r="1213" spans="1:2">
-      <c r="A1213" s="4"/>
-      <c r="B1213" s="5"/>
-    </row>
-    <row r="1214" spans="1:2">
-      <c r="A1214" s="4"/>
-      <c r="B1214" s="5"/>
-    </row>
-    <row r="1215" spans="1:2">
-      <c r="A1215" s="4"/>
-      <c r="B1215" s="5"/>
-    </row>
-    <row r="1216" spans="1:2">
-      <c r="A1216" s="4"/>
-      <c r="B1216" s="5"/>
-    </row>
-    <row r="1217" spans="1:2">
-      <c r="A1217" s="4"/>
-      <c r="B1217" s="5"/>
-    </row>
-    <row r="1218" spans="1:2">
-      <c r="A1218" s="4"/>
-      <c r="B1218" s="5"/>
-    </row>
-    <row r="1219" spans="1:2">
-      <c r="A1219" s="4"/>
-      <c r="B1219" s="5"/>
-    </row>
-    <row r="1220" spans="1:2">
-      <c r="A1220" s="4"/>
-      <c r="B1220" s="5"/>
-    </row>
-    <row r="1221" spans="1:2">
-      <c r="A1221" s="4"/>
-      <c r="B1221" s="5"/>
-    </row>
-    <row r="1222" spans="1:2">
-      <c r="A1222" s="4"/>
-      <c r="B1222" s="5"/>
-    </row>
-    <row r="1223" spans="1:2">
-      <c r="A1223" s="4"/>
-      <c r="B1223" s="5"/>
-    </row>
-    <row r="1224" spans="1:2">
-      <c r="A1224" s="4"/>
-      <c r="B1224" s="5"/>
-    </row>
-    <row r="1225" spans="1:2">
-      <c r="A1225" s="4"/>
-      <c r="B1225" s="5"/>
-    </row>
-    <row r="1226" spans="1:2">
-      <c r="A1226" s="4"/>
-      <c r="B1226" s="5"/>
-    </row>
-    <row r="1227" spans="1:2">
-      <c r="A1227" s="4"/>
-      <c r="B1227" s="5"/>
-    </row>
-    <row r="1228" spans="1:3">
-      <c r="A1228" s="1">
+    <row r="1143" spans="1:3">
+      <c r="A1143" s="1">
         <v>46280</v>
       </c>
-      <c r="B1228" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1228">
+      <c r="B1143" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1143">
         <v>330735</v>
       </c>
     </row>
-    <row r="1229" spans="1:3">
-      <c r="A1229" s="1">
+    <row r="1144" spans="1:3">
+      <c r="A1144" s="1">
         <v>46281</v>
       </c>
-      <c r="B1229" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1229">
+      <c r="B1144" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1144">
         <v>398760</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1228">
-    <sortState ref="A1:E1228">
+  <autoFilter ref="A1:E1144">
+    <sortState ref="A1:E1144">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2 B16 B3:B15 B17:B1142 B1143:B1227">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2 B16 B3:B15 B17:B1142">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1145</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,17 +203,29 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,28 +233,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,7 +257,68 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,23 +332,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,51 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +416,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,61 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,6 +608,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,20 +638,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,16 +655,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1145"/>
+  <dimension ref="A1:E1146"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16155,9 +16155,20 @@
         <v>365106</v>
       </c>
     </row>
+    <row r="1146" spans="1:3">
+      <c r="A1146" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1146">
+        <v>424583</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1144">
-    <sortState ref="A1:E1144">
+  <autoFilter ref="A1:E1145">
+    <sortState ref="A1:E1145">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1146</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,17 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,30 +227,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,22 +264,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -280,30 +271,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,17 +293,26 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,6 +321,29 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +422,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +470,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +571,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,21 +640,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -621,17 +649,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,175 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1146"/>
+  <dimension ref="A1:E1147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16166,9 +16166,20 @@
         <v>424583</v>
       </c>
     </row>
+    <row r="1147" spans="1:3">
+      <c r="A1147" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1147">
+        <v>424583</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1145">
-    <sortState ref="A1:E1145">
+  <autoFilter ref="A1:E1146">
+    <sortState ref="A1:E1146">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1147</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,31 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,8 +218,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,7 +235,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,7 +257,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,6 +293,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -293,18 +316,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,16 +332,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,49 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,6 +587,50 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -604,8 +648,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,211 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1147"/>
+  <dimension ref="A1:E1148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16177,9 +16177,20 @@
         <v>424583</v>
       </c>
     </row>
+    <row r="1148" spans="1:3">
+      <c r="A1148" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1148">
+        <v>350382</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1146">
-    <sortState ref="A1:E1146">
+  <autoFilter ref="A1:E1147">
+    <sortState ref="A1:E1147">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1148</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,36 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,14 +247,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,37 +269,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,33 +316,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -323,15 +332,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,55 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,49 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +464,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,46 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,15 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,167 +624,211 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1148"/>
+  <dimension ref="A1:E1149"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16188,9 +16188,20 @@
         <v>350382</v>
       </c>
     </row>
+    <row r="1149" spans="1:3">
+      <c r="A1149" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1149">
+        <v>345597</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1147">
-    <sortState ref="A1:E1147">
+  <autoFilter ref="A1:E1148">
+    <sortState ref="A1:E1148">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1149</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,22 +269,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,64 +300,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,6 +323,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,49 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,55 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,31 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,11 +604,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,6 +634,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -624,211 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1149"/>
+  <dimension ref="A1:E1150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16199,9 +16199,20 @@
         <v>345597</v>
       </c>
     </row>
+    <row r="1150" spans="1:3">
+      <c r="A1150" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1150">
+        <v>304531</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1148">
-    <sortState ref="A1:E1148">
+  <autoFilter ref="A1:E1149">
+    <sortState ref="A1:E1149">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1150</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,36 +225,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -256,37 +233,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,6 +247,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -307,11 +262,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,7 +294,38 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +334,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,25 +380,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,55 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,24 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -604,17 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,11 +612,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,7 +638,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +657,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1150"/>
+  <dimension ref="A1:E1151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16210,9 +16210,20 @@
         <v>304531</v>
       </c>
     </row>
+    <row r="1151" spans="1:3">
+      <c r="A1151" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1151">
+        <v>451473</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1149">
-    <sortState ref="A1:E1149">
+  <autoFilter ref="A1:E1150">
+    <sortState ref="A1:E1150">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1151</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,73 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,9 +226,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,16 +295,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,6 +319,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +404,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,73 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,37 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,6 +595,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -613,8 +633,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,15 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -657,84 +668,73 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -743,76 +743,76 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1151"/>
+  <dimension ref="A1:E1152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16221,9 +16221,20 @@
         <v>451473</v>
       </c>
     </row>
+    <row r="1152" spans="1:3">
+      <c r="A1152" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1152">
+        <v>372224</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1150">
-    <sortState ref="A1:E1150">
+  <autoFilter ref="A1:E1151">
+    <sortState ref="A1:E1151">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1152</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,37 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,16 +226,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,9 +258,31 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -303,29 +303,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +325,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +428,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,19 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,25 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -589,43 +598,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +628,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1152"/>
+  <dimension ref="A1:E1153"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16232,9 +16232,20 @@
         <v>372224</v>
       </c>
     </row>
+    <row r="1153" spans="1:3">
+      <c r="A1153" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1153">
+        <v>440442</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1151">
-    <sortState ref="A1:E1151">
+  <autoFilter ref="A1:E1152">
+    <sortState ref="A1:E1152">
       <sortCondition ref="A2:A1320"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AA33A6-4E03-4222-9817-6242E256EDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A2564B-FC1E-40B2-A7D9-DC99BF47966D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1154</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -736,7 +736,7 @@
   </sheetData>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -879,7 +879,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E1154"/>
+  <dimension ref="A1:E1155"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -15446,8 +15446,19 @@
         <v>324967</v>
       </c>
     </row>
+    <row r="1155" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1155" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1155" s="7">
+        <v>241074</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1153" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:E1154" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1156</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,99 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,10 +226,93 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,8 +325,16 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +434,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +482,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,79 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,8 +600,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,34 +654,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1156"/>
+  <dimension ref="A1:E1157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16077,8 +16077,19 @@
         <v>352688</v>
       </c>
     </row>
+    <row r="1157" spans="1:3">
+      <c r="A1157" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1157">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1155">
+  <autoFilter ref="A1:E1156">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C119E198-C690-4C1C-A659-8025F757C303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F80CEA-2059-4E99-9164-43AB6A4767F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,18 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1158</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -170,7 +181,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -185,23 +196,27 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
@@ -255,14 +270,14 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -11209,7 +11224,7 @@
         <v>33</v>
       </c>
       <c r="C794" s="5">
-        <v>8482645</v>
+        <v>1187071</v>
       </c>
       <c r="D794" s="5"/>
       <c r="E794" s="5"/>
@@ -11222,7 +11237,7 @@
         <v>33</v>
       </c>
       <c r="C795" s="5">
-        <v>4529868</v>
+        <v>1009380</v>
       </c>
       <c r="D795" s="5"/>
       <c r="E795" s="5"/>
@@ -11235,7 +11250,7 @@
         <v>33</v>
       </c>
       <c r="C796" s="5">
-        <v>21655309</v>
+        <v>612555</v>
       </c>
       <c r="D796" s="5"/>
       <c r="E796" s="5"/>
@@ -11248,7 +11263,7 @@
         <v>33</v>
       </c>
       <c r="C797" s="5">
-        <v>1365000</v>
+        <v>1556904</v>
       </c>
       <c r="D797" s="5"/>
       <c r="E797" s="5"/>
@@ -11261,7 +11276,7 @@
         <v>33</v>
       </c>
       <c r="C798" s="5">
-        <v>3974865</v>
+        <v>1693551</v>
       </c>
       <c r="D798" s="5"/>
       <c r="E798" s="5"/>
@@ -11274,7 +11289,7 @@
         <v>33</v>
       </c>
       <c r="C799" s="5">
-        <v>3656278</v>
+        <v>1294978</v>
       </c>
       <c r="D799" s="5"/>
       <c r="E799" s="5"/>
@@ -11287,7 +11302,7 @@
         <v>33</v>
       </c>
       <c r="C800" s="5">
-        <v>1441945</v>
+        <v>2129611</v>
       </c>
       <c r="D800" s="5"/>
       <c r="E800" s="5"/>
@@ -11300,7 +11315,7 @@
         <v>33</v>
       </c>
       <c r="C801" s="5">
-        <v>1719452</v>
+        <v>1372724</v>
       </c>
       <c r="D801" s="5"/>
       <c r="E801" s="5"/>
@@ -11313,7 +11328,7 @@
         <v>33</v>
       </c>
       <c r="C802" s="5">
-        <v>1387092</v>
+        <v>1292806</v>
       </c>
       <c r="D802" s="5"/>
       <c r="E802" s="5"/>
@@ -11326,7 +11341,7 @@
         <v>33</v>
       </c>
       <c r="C803" s="5">
-        <v>3636360</v>
+        <v>1588272</v>
       </c>
       <c r="D803" s="5"/>
       <c r="E803" s="5"/>
@@ -11339,7 +11354,7 @@
         <v>33</v>
       </c>
       <c r="C804" s="5">
-        <v>1701341</v>
+        <v>1040955</v>
       </c>
       <c r="D804" s="5"/>
       <c r="E804" s="5"/>
@@ -11352,7 +11367,7 @@
         <v>33</v>
       </c>
       <c r="C805" s="5">
-        <v>2253689</v>
+        <v>1206085</v>
       </c>
       <c r="D805" s="5"/>
       <c r="E805" s="5"/>
@@ -11365,7 +11380,7 @@
         <v>33</v>
       </c>
       <c r="C806" s="5">
-        <v>23077927</v>
+        <v>1332584</v>
       </c>
       <c r="D806" s="5"/>
       <c r="E806" s="5"/>
@@ -11378,7 +11393,7 @@
         <v>33</v>
       </c>
       <c r="C807" s="5">
-        <v>1449010</v>
+        <v>1560265</v>
       </c>
       <c r="D807" s="5"/>
       <c r="E807" s="5"/>
@@ -11391,7 +11406,7 @@
         <v>33</v>
       </c>
       <c r="C808" s="5">
-        <v>1513852</v>
+        <v>1419051</v>
       </c>
       <c r="D808" s="5"/>
       <c r="E808" s="5"/>
@@ -11404,7 +11419,7 @@
         <v>33</v>
       </c>
       <c r="C809" s="5">
-        <v>4787941</v>
+        <v>1382462</v>
       </c>
       <c r="D809" s="5"/>
       <c r="E809" s="5"/>
@@ -11417,7 +11432,7 @@
         <v>33</v>
       </c>
       <c r="C810" s="5">
-        <v>3467841</v>
+        <v>870232</v>
       </c>
       <c r="D810" s="5"/>
       <c r="E810" s="5"/>
@@ -11430,7 +11445,7 @@
         <v>33</v>
       </c>
       <c r="C811" s="5">
-        <v>1553157</v>
+        <v>1013914</v>
       </c>
       <c r="D811" s="5"/>
       <c r="E811" s="5"/>
@@ -11443,7 +11458,7 @@
         <v>33</v>
       </c>
       <c r="C812" s="5">
-        <v>3349181</v>
+        <v>1350893</v>
       </c>
       <c r="D812" s="5"/>
       <c r="E812" s="5"/>
@@ -11456,7 +11471,7 @@
         <v>33</v>
       </c>
       <c r="C813" s="5">
-        <v>3693865</v>
+        <v>1339720</v>
       </c>
       <c r="D813" s="5"/>
       <c r="E813" s="5"/>
@@ -11469,7 +11484,7 @@
         <v>33</v>
       </c>
       <c r="C814" s="5">
-        <v>1711682</v>
+        <v>1077354</v>
       </c>
       <c r="D814" s="5"/>
       <c r="E814" s="5"/>
@@ -11482,7 +11497,7 @@
         <v>33</v>
       </c>
       <c r="C815" s="5">
-        <v>1209081</v>
+        <v>875239</v>
       </c>
       <c r="D815" s="5"/>
       <c r="E815" s="5"/>
@@ -11495,7 +11510,7 @@
         <v>33</v>
       </c>
       <c r="C816" s="5">
-        <v>21150645</v>
+        <v>874564</v>
       </c>
       <c r="D816" s="5"/>
       <c r="E816" s="5"/>
@@ -11508,7 +11523,7 @@
         <v>33</v>
       </c>
       <c r="C817" s="5">
-        <v>1134268</v>
+        <v>758179</v>
       </c>
       <c r="D817" s="5"/>
       <c r="E817" s="5"/>
@@ -11521,7 +11536,7 @@
         <v>33</v>
       </c>
       <c r="C818" s="5">
-        <v>1370393</v>
+        <v>718823</v>
       </c>
       <c r="D818" s="5"/>
       <c r="E818" s="5"/>
@@ -11534,7 +11549,7 @@
         <v>33</v>
       </c>
       <c r="C819" s="5">
-        <v>1340384</v>
+        <v>999607</v>
       </c>
       <c r="D819" s="5"/>
       <c r="E819" s="5"/>
@@ -11547,7 +11562,7 @@
         <v>33</v>
       </c>
       <c r="C820" s="5">
-        <v>4599748</v>
+        <v>1332289</v>
       </c>
       <c r="D820" s="5"/>
       <c r="E820" s="5"/>
@@ -11560,7 +11575,7 @@
         <v>33</v>
       </c>
       <c r="C821" s="5">
-        <v>3448950</v>
+        <v>1741157</v>
       </c>
       <c r="D821" s="5"/>
       <c r="E821" s="5"/>
@@ -11573,7 +11588,7 @@
         <v>33</v>
       </c>
       <c r="C822" s="5">
-        <v>1267342</v>
+        <v>1554472</v>
       </c>
       <c r="D822" s="5"/>
       <c r="E822" s="5"/>
@@ -11586,7 +11601,7 @@
         <v>33</v>
       </c>
       <c r="C823" s="5">
-        <v>3053645</v>
+        <v>1693881</v>
       </c>
       <c r="D823" s="5"/>
       <c r="E823" s="5"/>
@@ -11599,7 +11614,7 @@
         <v>33</v>
       </c>
       <c r="C824" s="5">
-        <v>2533745</v>
+        <v>1253801</v>
       </c>
       <c r="D824" s="5"/>
       <c r="E824" s="5"/>

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1160</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,61 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,47 +279,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -282,36 +295,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,16 +310,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,6 +329,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +416,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,37 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,7 +631,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,22 +649,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1160"/>
+  <dimension ref="A1:E1161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16121,8 +16121,16 @@
         <v>633888</v>
       </c>
     </row>
+    <row r="1161" spans="1:2">
+      <c r="A1161" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1159">
+  <autoFilter ref="A1:E1160">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1162</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,26 +204,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -243,7 +227,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,21 +280,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -280,15 +287,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -310,7 +325,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,22 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,163 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +525,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,32 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,15 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -640,11 +610,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +640,31 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1162"/>
+  <dimension ref="A1:E1163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16143,8 +16143,19 @@
         <v>756334</v>
       </c>
     </row>
+    <row r="1163" spans="1:3">
+      <c r="A1163" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1163">
+        <v>712390</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1161">
+  <autoFilter ref="A1:E1162">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1163</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -203,17 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,21 +239,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -255,70 +246,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,8 +269,79 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +386,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,103 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,6 +595,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -606,6 +630,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,197 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1163"/>
+  <dimension ref="A1:E1164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16154,8 +16154,19 @@
         <v>712390</v>
       </c>
     </row>
+    <row r="1164" spans="1:3">
+      <c r="A1164" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1164">
+        <v>545939</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1162">
+  <autoFilter ref="A1:E1163">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1164</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,7 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,15 +269,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,39 +316,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -316,16 +331,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +410,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,25 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,19 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,47 +619,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +642,29 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1164"/>
+  <dimension ref="A1:E1165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16165,8 +16165,19 @@
         <v>545939</v>
       </c>
     </row>
+    <row r="1165" spans="1:3">
+      <c r="A1165" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1165">
+        <v>420687</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1163">
+  <autoFilter ref="A1:E1164">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1165</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,43 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -212,7 +249,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,44 +287,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,24 +310,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,25 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,49 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,37 +488,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,54 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,54 +649,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1165"/>
+  <dimension ref="A1:E1166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16176,8 +16176,16 @@
         <v>420687</v>
       </c>
     </row>
+    <row r="1166" spans="1:2">
+      <c r="A1166" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1164">
+  <autoFilter ref="A1:E1165">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1167</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,40 +233,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,14 +256,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,7 +302,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -317,33 +310,40 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,6 +362,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,127 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +476,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -606,35 +586,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +626,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1167"/>
+  <dimension ref="A1:E1168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16198,8 +16198,19 @@
         <v>448527</v>
       </c>
     </row>
+    <row r="1168" spans="1:3">
+      <c r="A1168" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1168">
+        <v>510260</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1166">
+  <autoFilter ref="A1:E1167">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1168</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -204,7 +204,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,6 +250,29 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,8 +286,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,55 +309,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,20 +324,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -325,25 +333,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,31 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,31 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -588,11 +603,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,21 +640,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -636,25 +649,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1168"/>
+  <dimension ref="A1:E1169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16209,8 +16209,19 @@
         <v>510260</v>
       </c>
     </row>
+    <row r="1169" spans="1:3">
+      <c r="A1169" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1169">
+        <v>461766</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1167">
+  <autoFilter ref="A1:E1168">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1169</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,13 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -218,7 +211,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,7 +270,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -248,31 +293,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,38 +309,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,8 +324,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,49 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,48 +440,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -536,13 +452,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -586,17 +601,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,7 +614,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,6 +630,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,29 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1169"/>
+  <dimension ref="A1:E1170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16220,8 +16220,19 @@
         <v>461766</v>
       </c>
     </row>
+    <row r="1170" spans="1:3">
+      <c r="A1170" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1170">
+        <v>487455</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1168">
+  <autoFilter ref="A1:E1169">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1170</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,15 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,6 +219,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,29 +258,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,22 +286,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -294,8 +295,23 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,17 +332,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +392,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +434,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,85 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,48 +593,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +614,57 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1170"/>
+  <dimension ref="A1:E1171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16231,8 +16231,19 @@
         <v>487455</v>
       </c>
     </row>
+    <row r="1171" spans="1:3">
+      <c r="A1171" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1171">
+        <v>487455</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1169">
+  <autoFilter ref="A1:E1170">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1171</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,58 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,68 +271,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,15 +302,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,15 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,7 +368,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,43 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +482,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,20 +610,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,24 +642,29 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1171"/>
+  <dimension ref="A1:E1172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16242,8 +16242,16 @@
         <v>487455</v>
       </c>
     </row>
+    <row r="1172" spans="1:2">
+      <c r="A1172" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1170">
+  <autoFilter ref="A1:E1171">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1174</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,24 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,8 +220,15 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,8 +242,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,8 +271,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,7 +318,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,59 +344,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +410,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,43 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,31 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -596,16 +581,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,28 +613,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +642,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1174"/>
+  <dimension ref="A1:E1175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16275,8 +16275,19 @@
         <v>348312</v>
       </c>
     </row>
+    <row r="1175" spans="1:3">
+      <c r="A1175" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1175">
+        <v>558831</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1173">
+  <autoFilter ref="A1:E1174">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1176</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,22 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,7 +241,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,68 +263,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,7 +279,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,9 +316,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +325,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,37 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,43 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -599,7 +599,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,8 +618,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,21 +655,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -657,33 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1175"/>
+  <dimension ref="A1:E1177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16286,8 +16286,27 @@
         <v>558831</v>
       </c>
     </row>
+    <row r="1176" spans="1:3">
+      <c r="A1176" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1176">
+        <v>558831</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:2">
+      <c r="A1177" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1174">
+  <autoFilter ref="A1:E1176">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1178</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,9 +224,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,16 +240,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,15 +255,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,8 +286,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -327,21 +342,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,25 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +494,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,30 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +634,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1178"/>
+  <dimension ref="A1:E1179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16319,8 +16319,19 @@
         <v>455952</v>
       </c>
     </row>
+    <row r="1179" spans="1:3">
+      <c r="A1179" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1179">
+        <v>582093</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1177">
+  <autoFilter ref="A1:E1178">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1179</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,30 +226,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,11 +248,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -270,24 +271,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,7 +295,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,31 +340,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +428,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,25 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -582,15 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,22 +620,36 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,171 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1179"/>
+  <dimension ref="A1:E1180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16330,8 +16330,19 @@
         <v>582093</v>
       </c>
     </row>
+    <row r="1180" spans="1:3">
+      <c r="A1180" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1180">
+        <v>371772</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1178">
+  <autoFilter ref="A1:E1179">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1180</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,76 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,13 +227,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -309,8 +235,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,11 +301,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,9 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,24 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -392,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +416,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,6 +621,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -620,36 +649,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1180"/>
+  <dimension ref="A1:E1181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16341,8 +16341,19 @@
         <v>371772</v>
       </c>
     </row>
+    <row r="1181" spans="1:3">
+      <c r="A1181" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1181">
+        <v>413539</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1179">
+  <autoFilter ref="A1:E1180">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1181</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,11 +203,86 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,9 +294,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,14 +332,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -251,97 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +392,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,37 +458,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,55 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,35 +573,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,23 +613,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,6 +635,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1181"/>
+  <dimension ref="A1:E1182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16352,8 +16352,19 @@
         <v>413539</v>
       </c>
     </row>
+    <row r="1182" spans="1:3">
+      <c r="A1182" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1182">
+        <v>421823</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1180">
+  <autoFilter ref="A1:E1181">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1182</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,89 +212,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,6 +227,97 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -340,8 +333,15 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +404,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,31 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,19 +615,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,6 +626,30 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,179 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1182"/>
+  <dimension ref="A1:E1183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16363,8 +16363,19 @@
         <v>421823</v>
       </c>
     </row>
+    <row r="1183" spans="1:3">
+      <c r="A1183" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1183">
+        <v>357159</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1181">
+  <autoFilter ref="A1:E1182">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1184</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -204,7 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,9 +217,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,30 +240,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,8 +278,39 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,47 +331,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,85 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +476,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,17 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,8 +604,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,15 +615,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +648,184 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1183"/>
+  <dimension ref="A1:E1185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16374,8 +16374,27 @@
         <v>357159</v>
       </c>
     </row>
+    <row r="1184" spans="1:3">
+      <c r="A1184" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1184">
+        <v>357159</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1182">
+  <autoFilter ref="A1:E1184">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1187</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,19 +211,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -235,7 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,29 +293,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,35 +308,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -334,7 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +398,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,25 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,21 +581,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -606,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,17 +615,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,16 +653,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -686,7 +686,7 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,121 +695,121 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -818,14 +818,14 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1187"/>
+  <dimension ref="A1:E1188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16418,8 +16418,19 @@
         <v>442851</v>
       </c>
     </row>
+    <row r="1188" spans="1:3">
+      <c r="A1188" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1188">
+        <v>598034</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1186">
+  <autoFilter ref="A1:E1187">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1188</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,38 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,7 +243,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,22 +273,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,7 +288,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,7 +302,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,6 +310,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -293,50 +332,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,7 +374,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,37 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,31 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,37 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,26 +639,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -635,21 +650,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1188"/>
+  <dimension ref="A1:E1189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16429,8 +16429,19 @@
         <v>598034</v>
       </c>
     </row>
+    <row r="1189" spans="1:3">
+      <c r="A1189" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1189">
+        <v>486246</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1187">
+  <autoFilter ref="A1:E1188">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1189</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,37 +204,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -249,46 +218,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,7 +241,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,9 +286,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,8 +331,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,18 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -386,7 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +404,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,49 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,25 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,54 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,41 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -630,11 +595,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +634,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1189"/>
+  <dimension ref="A1:E1190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16440,8 +16440,19 @@
         <v>486246</v>
       </c>
     </row>
+    <row r="1190" spans="1:3">
+      <c r="A1190" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1190">
+        <v>378006</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1188">
+  <autoFilter ref="A1:E1189">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/amazon.xlsx
+++ b/dashboard/data/incoming/amazon.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1190</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,27 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -211,52 +232,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,7 +250,44 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,38 +301,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,9 +317,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +334,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,31 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,31 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +482,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +602,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,199 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,7 +1488,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1190"/>
+  <dimension ref="A1:E1191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -16451,8 +16451,19 @@
         <v>378006</v>
       </c>
     </row>
+    <row r="1191" spans="1:3">
+      <c r="A1191" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1191">
+        <v>374764</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1189">
+  <autoFilter ref="A1:E1190">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
